--- a/maternal-portal-data.xlsx
+++ b/maternal-portal-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krrish Bagaria\Downloads\MaternalProject\maternal-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999E4862-150D-470B-BC79-D9A55A508158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91000B98-0080-48EA-8897-94D7C54866CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
   <si>
     <t>Patient ID</t>
   </si>
@@ -32,79 +32,70 @@
     <t>Contact</t>
   </si>
   <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
     <t>Due Date</t>
   </si>
   <si>
-    <t>Last Week Sent</t>
+    <t>First Appointment</t>
+  </si>
+  <si>
+    <t>Last Appointment</t>
+  </si>
+  <si>
+    <t>Diagnosis</t>
+  </si>
+  <si>
+    <t>Remarks</t>
   </si>
   <si>
     <t>Active</t>
   </si>
   <si>
-    <t>00001</t>
-  </si>
-  <si>
-    <t>Krrish</t>
+    <t>100001</t>
+  </si>
+  <si>
+    <t>Krrish Bagaria</t>
   </si>
   <si>
     <t>9819815966</t>
   </si>
   <si>
+    <t>Pregnancy</t>
+  </si>
+  <si>
+    <t>Bro is pregnant fr</t>
+  </si>
+  <si>
+    <t>Bro crazy</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>100002</t>
+  </si>
+  <si>
+    <t>Bruh</t>
+  </si>
+  <si>
+    <t>9819818854</t>
+  </si>
+  <si>
+    <t>Condition 6</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>00002</t>
-  </si>
-  <si>
-    <t>Prachee</t>
-  </si>
-  <si>
-    <t>9819817885</t>
-  </si>
-  <si>
-    <t>19/11/03</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>P-3</t>
-  </si>
-  <si>
-    <t>Bruh</t>
-  </si>
-  <si>
-    <t>9819815967</t>
-  </si>
-  <si>
-    <t>25/05/23</t>
-  </si>
-  <si>
-    <t>P-4</t>
-  </si>
-  <si>
-    <t>Vaibhav Singh</t>
-  </si>
-  <si>
-    <t>9967583596</t>
-  </si>
-  <si>
-    <t>09/12/26</t>
-  </si>
-  <si>
-    <t>P-5</t>
-  </si>
-  <si>
-    <t>Arnav Deshpande</t>
-  </si>
-  <si>
-    <t>6969696969</t>
-  </si>
-  <si>
-    <t>23/04/025</t>
+    <t>Bruh Moment</t>
+  </si>
+  <si>
+    <t>Moment Bruh</t>
   </si>
   <si>
     <t>Week</t>
@@ -231,31 +222,16 @@
   </si>
   <si>
     <t>Week 40 — Please add the health guidance message for this week.</t>
-  </si>
-  <si>
-    <t>P-6</t>
-  </si>
-  <si>
-    <t>Bruh Moment</t>
-  </si>
-  <si>
-    <t>23/04/026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -623,18 +599,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="10" width="30.83203125" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -653,129 +632,96 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1">
-        <v>38893</v>
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46198</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46073</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46078</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7">
-        <v>9819815686</v>
-      </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 A3:F6 A2:C2 E2:F2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -791,10 +737,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -802,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -810,7 +756,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -818,7 +764,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -826,7 +772,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -834,7 +780,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -842,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -850,7 +796,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -858,7 +804,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -866,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -874,7 +820,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -882,7 +828,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -890,7 +836,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -898,7 +844,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -906,7 +852,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -914,7 +860,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -922,7 +868,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -930,7 +876,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -938,7 +884,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -946,7 +892,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -954,7 +900,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -962,7 +908,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -970,7 +916,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -978,7 +924,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -986,7 +932,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -994,7 +940,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1002,7 +948,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1010,7 +956,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1018,7 +964,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1026,7 +972,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1034,7 +980,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1042,7 +988,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1050,7 +996,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1058,7 +1004,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1066,7 +1012,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1074,7 +1020,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1082,7 +1028,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1090,7 +1036,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1098,7 +1044,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1106,7 +1052,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
@@ -1114,7 +1060,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
